--- a/DOCP_optimization_3bus_example.xlsx
+++ b/DOCP_optimization_3bus_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pm.deoliveiradejes/Dropbox (Personal)/Ongoing Research/software3/Urda3bus_dynamicchanges/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pm.deoliveiradejes\Dropbox\Research\67new\superado\DOCP_67_Simulator_Optimizar - copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA37032-9C96-3847-A1C9-249A559233A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4C9F3-7AFE-4FB4-95DB-7DF6234A6BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="780" windowWidth="37920" windowHeight="23220" activeTab="1" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
   </bookViews>
   <sheets>
     <sheet name="Three_bus_without_transients" sheetId="4" r:id="rId1"/>
@@ -33,24 +33,27 @@
     <definedName name="pick5">Three_bus_with_transients!$AC$10</definedName>
     <definedName name="pick6" localSheetId="0">Three_bus_without_transients!$R$13</definedName>
     <definedName name="pick6">Three_bus_with_transients!$AC$11</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26,Three_bus_with_transients!$AC$2:$AC$3</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$AC$2:$AC$3</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Three_bus_with_transients!$S$21:$S$32</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">Three_bus_without_transients!$S$21:$S$26</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">Three_bus_with_transients!$S$21:$S$32</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$U$21:$U$26</definedName>
+    <definedName name="solver_lhs6" localSheetId="1" hidden="1">Three_bus_with_transients!$Z$2:$Z$3</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
@@ -60,11 +63,11 @@
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">6</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
@@ -76,16 +79,22 @@
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">1.1</definedName>
+    <definedName name="solver_rel4" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel5" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$AD$2:$AD$3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">1.1</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">0.1</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">11</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.1</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">0.2</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">0.2</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">0.2</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$V$21:$V$26</definedName>
+    <definedName name="solver_rhs6" localSheetId="1" hidden="1">Three_bus_with_transients!$AC$2:$AC$3</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
@@ -98,7 +107,7 @@
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
@@ -115,17 +124,23 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="55">
   <si>
     <t>B</t>
   </si>
@@ -421,6 +436,12 @@
   <si>
     <t>T422_0=</t>
   </si>
+  <si>
+    <t>tcritico</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
 </sst>
 </file>
 
@@ -431,7 +452,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -595,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -780,6 +801,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -825,8 +849,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8793843" y="587828"/>
-          <a:ext cx="4716709" cy="1987634"/>
+          <a:off x="8797018" y="581478"/>
+          <a:ext cx="4723059" cy="1955884"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -9821,8 +9845,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7496024" y="7237488"/>
-          <a:ext cx="4732735" cy="1966467"/>
+          <a:off x="7522482" y="7144884"/>
+          <a:ext cx="4722152" cy="1940009"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -18702,9 +18726,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -18742,7 +18766,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -18848,7 +18872,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -18990,7 +19014,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -19002,33 +19026,33 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:Y37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="1.1640625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
-    <col min="3" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="15" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="1.125" customWidth="1"/>
+    <col min="2" max="2" width="8.375" customWidth="1"/>
+    <col min="3" max="10" width="4.375" customWidth="1"/>
+    <col min="11" max="15" width="7.625" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.6640625" customWidth="1"/>
-    <col min="19" max="22" width="8.83203125" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" customWidth="1"/>
-    <col min="24" max="25" width="6.1640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.625" customWidth="1"/>
+    <col min="19" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="9.875" customWidth="1"/>
+    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.1640625" customWidth="1"/>
+    <col min="28" max="28" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:25">
       <c r="B1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:25">
       <c r="B2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:25">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -19038,7 +19062,7 @@
       <c r="R3" s="61"/>
       <c r="S3" s="61"/>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:25">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -19079,7 +19103,7 @@
       <c r="X4"/>
       <c r="Y4"/>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:25">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -19134,7 +19158,7 @@
       <c r="X5"/>
       <c r="Y5"/>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:25">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -19185,7 +19209,7 @@
       <c r="X6"/>
       <c r="Y6"/>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -19239,7 +19263,7 @@
       <c r="X7"/>
       <c r="Y7"/>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:25">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -19296,7 +19320,7 @@
       <c r="X8"/>
       <c r="Y8"/>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:25">
       <c r="Q9">
         <v>2</v>
       </c>
@@ -19306,7 +19330,7 @@
       <c r="X9"/>
       <c r="Y9"/>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:25">
       <c r="Q10">
         <v>3</v>
       </c>
@@ -19316,7 +19340,7 @@
       <c r="X10"/>
       <c r="Y10"/>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:25">
       <c r="Q11">
         <v>4</v>
       </c>
@@ -19326,7 +19350,7 @@
       <c r="X11"/>
       <c r="Y11"/>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:25">
       <c r="Q12">
         <v>5</v>
       </c>
@@ -19336,7 +19360,7 @@
       <c r="X12"/>
       <c r="Y12"/>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:25">
       <c r="Q13">
         <v>6</v>
       </c>
@@ -19346,11 +19370,11 @@
       <c r="X13"/>
       <c r="Y13"/>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:25">
       <c r="X14"/>
       <c r="Y14"/>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:25">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -19401,7 +19425,7 @@
       <c r="X15"/>
       <c r="Y15"/>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:25">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -19452,7 +19476,7 @@
       <c r="X16"/>
       <c r="Y16"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:25">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -19503,10 +19527,10 @@
       <c r="X17"/>
       <c r="Y17"/>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:25">
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:25">
       <c r="S19" s="1"/>
       <c r="T19" s="61" t="s">
         <v>22</v>
@@ -19515,7 +19539,7 @@
       <c r="V19" s="61"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:25">
       <c r="K20" s="59" t="s">
         <v>0</v>
       </c>
@@ -19534,7 +19558,7 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:25">
       <c r="J21">
         <v>1</v>
       </c>
@@ -19575,7 +19599,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:25">
       <c r="J22">
         <v>2</v>
       </c>
@@ -19615,7 +19639,7 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:25">
       <c r="J23">
         <v>3</v>
       </c>
@@ -19658,7 +19682,7 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:25">
       <c r="J24">
         <v>4</v>
       </c>
@@ -19698,7 +19722,7 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:25">
       <c r="J25">
         <v>5</v>
       </c>
@@ -19738,7 +19762,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:25">
       <c r="J26">
         <v>6</v>
       </c>
@@ -19778,7 +19802,7 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:25">
       <c r="T28" s="6" t="s">
         <v>46</v>
       </c>
@@ -19787,17 +19811,17 @@
         <v>2.0613271630758909</v>
       </c>
     </row>
-    <row r="33" spans="18:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="18:21">
       <c r="U33" s="1"/>
     </row>
-    <row r="35" spans="18:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="18:21">
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="18:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="18:21">
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="18:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="18:21">
       <c r="U37" s="1"/>
     </row>
   </sheetData>
@@ -19821,24 +19845,24 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B1:AC36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:AD36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="1.1640625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
-    <col min="3" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="15" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="1.125" customWidth="1"/>
+    <col min="2" max="2" width="8.375" customWidth="1"/>
+    <col min="3" max="10" width="4.375" customWidth="1"/>
+    <col min="11" max="15" width="7.625" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.6640625" customWidth="1"/>
-    <col min="19" max="22" width="8.83203125" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" customWidth="1"/>
-    <col min="24" max="25" width="6.1640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.625" customWidth="1"/>
+    <col min="19" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="9.875" customWidth="1"/>
+    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.1640625" customWidth="1"/>
+    <col min="28" max="28" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:30">
       <c r="B1" t="s">
         <v>34</v>
       </c>
@@ -19847,29 +19871,47 @@
       </c>
       <c r="AC1" s="61"/>
     </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:30">
       <c r="B2" t="s">
         <v>31</v>
       </c>
+      <c r="Z2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>54</v>
+      </c>
       <c r="AB2" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="AC2" s="9">
+      <c r="AC2" s="64">
         <v>0.14000000000000001</v>
       </c>
+      <c r="AD2">
+        <v>0.14000000000000001</v>
+      </c>
     </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:30">
       <c r="B3" t="s">
         <v>30</v>
       </c>
+      <c r="Z3">
+        <v>0.02</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>54</v>
+      </c>
       <c r="AB3" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AC3" s="9">
+      <c r="AC3" s="64">
         <v>0.02</v>
       </c>
+      <c r="AD3">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:30">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -19920,7 +19962,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:30">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -20000,7 +20042,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:30">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -20089,7 +20131,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:30">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -20178,7 +20220,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:30">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -20267,7 +20309,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:30">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -20356,7 +20398,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:30">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -20445,7 +20487,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:30">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -20534,7 +20576,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:30">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -20617,7 +20659,7 @@
         <v>-1.3391316716759885</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:30">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -20700,7 +20742,7 @@
         <v>-2.5273619887352097</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:30">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -20783,7 +20825,7 @@
         <v>-1.8483288249870145</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:30">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -20866,7 +20908,7 @@
         <v>-5.5079185398582702</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:30">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -20949,7 +20991,7 @@
         <v>-2.7474032970096647</v>
       </c>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:26">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -21032,17 +21074,17 @@
         <v>-2.9021268406640557</v>
       </c>
     </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:26">
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:26">
       <c r="U19" s="63" t="s">
         <v>22</v>
       </c>
       <c r="V19" s="63"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:26">
       <c r="C20" t="s">
         <v>24</v>
       </c>
@@ -21060,9 +21102,12 @@
       <c r="S20" s="10" t="s">
         <v>1</v>
       </c>
+      <c r="V20" t="s">
+        <v>53</v>
+      </c>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:26">
       <c r="C21" t="s">
         <v>38</v>
       </c>
@@ -21073,8 +21118,8 @@
         <v>1</v>
       </c>
       <c r="K21" s="11">
-        <f>-Z9</f>
-        <v>2.2105209071486667</v>
+        <f>W9</f>
+        <v>-2.7691675289173658</v>
       </c>
       <c r="L21" s="12">
         <f>-Q9</f>
@@ -21098,7 +21143,7 @@
       </c>
       <c r="S21" s="19">
         <f t="array" ref="S21:S32">MMULT(K21:P32,Q21:Q26)</f>
-        <v>0.88395972209149831</v>
+        <v>0.32163183147068763</v>
       </c>
       <c r="T21" s="57" t="s">
         <v>47</v>
@@ -21107,10 +21152,12 @@
         <f>-Q22*L28</f>
         <v>0.33338870753021377</v>
       </c>
-      <c r="V21" s="8"/>
+      <c r="V21" s="8">
+        <v>0.5</v>
+      </c>
       <c r="W21" s="8"/>
     </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:26">
       <c r="C22" t="s">
         <v>37</v>
       </c>
@@ -21150,10 +21197,12 @@
         <f>-K22*Q21</f>
         <v>0.27326331255219577</v>
       </c>
-      <c r="V22" s="9"/>
+      <c r="V22" s="8">
+        <v>0.5</v>
+      </c>
       <c r="W22" s="9"/>
     </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:26">
       <c r="C23" t="s">
         <v>39</v>
       </c>
@@ -21197,10 +21246,12 @@
         <f>Q24*O16</f>
         <v>0.48487038977007496</v>
       </c>
-      <c r="V23" s="8"/>
+      <c r="V23" s="8">
+        <v>0.5</v>
+      </c>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:26">
       <c r="C24" t="s">
         <v>37</v>
       </c>
@@ -21240,10 +21291,12 @@
         <f>-M24*Q23</f>
         <v>0.42908147743086456</v>
       </c>
-      <c r="V24" s="9"/>
+      <c r="V24" s="8">
+        <v>0.5</v>
+      </c>
       <c r="W24" s="9"/>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:26">
       <c r="C25" t="s">
         <v>38</v>
       </c>
@@ -21287,10 +21340,12 @@
         <f>-P32*Q26</f>
         <v>0.32151038697485096</v>
       </c>
-      <c r="V25" s="8"/>
+      <c r="V25" s="8">
+        <v>0.5</v>
+      </c>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:26">
       <c r="C26" t="s">
         <v>37</v>
       </c>
@@ -21330,8 +21385,11 @@
         <f>-O26*Q25</f>
         <v>0.26753186866431033</v>
       </c>
+      <c r="V26" s="8">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:26">
       <c r="C27" t="s">
         <v>38</v>
       </c>
@@ -21366,7 +21424,7 @@
         <v>0.70004040540572343</v>
       </c>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:26">
       <c r="C28" t="s">
         <v>37</v>
       </c>
@@ -21397,7 +21455,7 @@
         <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:26">
       <c r="C29" t="s">
         <v>39</v>
       </c>
@@ -21429,7 +21487,7 @@
         <v>0.1999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:26">
       <c r="C30" t="s">
         <v>37</v>
       </c>
@@ -21460,7 +21518,7 @@
         <v>0.35595039650151911</v>
       </c>
     </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:26">
       <c r="C31" t="s">
         <v>38</v>
       </c>
@@ -21495,7 +21553,7 @@
         <v>0.97063504577823023</v>
       </c>
     </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:26">
       <c r="C32" t="s">
         <v>37</v>
       </c>
@@ -21526,7 +21584,7 @@
         <v>0.20000000000000012</v>
       </c>
     </row>
-    <row r="35" spans="18:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="18:23">
       <c r="U35" s="6" t="s">
         <v>21</v>
       </c>
@@ -21535,7 +21593,7 @@
         <v>2.1096461429225104</v>
       </c>
     </row>
-    <row r="36" spans="18:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="18:23">
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -21545,17 +21603,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="K20:P20"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/DOCP_optimization_3bus_example.xlsx
+++ b/DOCP_optimization_3bus_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pm.deoliveiradejes\Dropbox\Research\67new\superado\DOCP_67_Simulator_Optimizar - copia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\GitHub\Optimal_DOCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4C9F3-7AFE-4FB4-95DB-7DF6234A6BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F7E2EF-78E9-455A-8CF4-9C57A4110E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
   </bookViews>
   <sheets>
     <sheet name="Three_bus_without_transients" sheetId="4" r:id="rId1"/>
@@ -33,26 +33,26 @@
     <definedName name="pick5">Three_bus_with_transients!$AC$10</definedName>
     <definedName name="pick6" localSheetId="0">Three_bus_without_transients!$R$13</definedName>
     <definedName name="pick6">Three_bus_with_transients!$AC$11</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26,Three_bus_with_transients!$AC$2:$AC$3</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$AC$2:$AC$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">Three_bus_without_transients!$Q$21:$Q$26</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Three_bus_with_transients!$Q$21:$Q$26</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Three_bus_with_transients!$S$21:$S$32</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">Three_bus_without_transients!$S$21:$S$26</definedName>
     <definedName name="solver_lhs4" localSheetId="1" hidden="1">Three_bus_with_transients!$S$21:$S$32</definedName>
-    <definedName name="solver_lhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$U$21:$U$26</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$Z$2:$Z$3</definedName>
     <definedName name="solver_lhs6" localSheetId="1" hidden="1">Three_bus_with_transients!$Z$2:$Z$3</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
@@ -67,7 +67,7 @@
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">6</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
@@ -79,21 +79,21 @@
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel6" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$AD$2:$AD$3</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1.1</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">11</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.1</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">0.2</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">0.2</definedName>
-    <definedName name="solver_rhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$V$21:$V$26</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">Three_bus_with_transients!$U$28</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">Three_bus_without_transients!$R$15</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">Three_bus_with_transients!$U$29</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Three_bus_without_transients!$R$16</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">Three_bus_with_transients!$U$30</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">Three_bus_without_transients!$R$17</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">Three_bus_with_transients!$U$30</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">Three_bus_with_transients!$AC$2:$AC$3</definedName>
     <definedName name="solver_rhs6" localSheetId="1" hidden="1">Three_bus_with_transients!$AC$2:$AC$3</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
@@ -108,7 +108,7 @@
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
@@ -132,15 +132,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="57">
   <si>
     <t>B</t>
   </si>
@@ -437,10 +434,16 @@
     <t>T422_0=</t>
   </si>
   <si>
-    <t>tcritico</t>
+    <t>&lt;</t>
   </si>
   <si>
-    <t>&lt;</t>
+    <t>Dmax</t>
+  </si>
+  <si>
+    <t>Dmin</t>
+  </si>
+  <si>
+    <t>CTI</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -786,6 +789,12 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -800,9 +809,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,8 +855,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8797018" y="581478"/>
-          <a:ext cx="4723059" cy="1955884"/>
+          <a:off x="8743043" y="575128"/>
+          <a:ext cx="4697659" cy="1924134"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -9845,8 +9851,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7522482" y="7144884"/>
-          <a:ext cx="4722152" cy="1940009"/>
+          <a:off x="7469565" y="7052279"/>
+          <a:ext cx="4700986" cy="1913551"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -18726,7 +18732,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -19026,20 +19032,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:Y37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="1.125" customWidth="1"/>
-    <col min="2" max="2" width="8.375" customWidth="1"/>
-    <col min="3" max="10" width="4.375" customWidth="1"/>
-    <col min="11" max="15" width="7.625" customWidth="1"/>
+    <col min="1" max="1" width="1.08203125" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="3" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="15" width="7.58203125" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.625" customWidth="1"/>
-    <col min="19" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="9.875" customWidth="1"/>
-    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.58203125" customWidth="1"/>
+    <col min="19" max="22" width="8.83203125" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" customWidth="1"/>
+    <col min="24" max="25" width="6.08203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.58203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.125" customWidth="1"/>
+    <col min="28" max="28" width="5.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
@@ -19056,11 +19062,11 @@
       <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="61"/>
-      <c r="S3" s="61"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
     </row>
     <row r="4" spans="2:25">
       <c r="B4" s="3" t="s">
@@ -19074,26 +19080,26 @@
         <v>25</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62" t="s">
+      <c r="J4" s="64"/>
+      <c r="K4" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="62"/>
-      <c r="M4" s="60" t="s">
+      <c r="L4" s="64"/>
+      <c r="M4" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60" t="s">
+      <c r="N4" s="62"/>
+      <c r="O4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="60"/>
+      <c r="P4" s="62"/>
       <c r="Q4" s="48" t="s">
         <v>35</v>
       </c>
@@ -19422,6 +19428,12 @@
       <c r="P15" s="29">
         <v>-85.715535882699896</v>
       </c>
+      <c r="Q15" t="s">
+        <v>54</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="X15"/>
       <c r="Y15"/>
     </row>
@@ -19473,6 +19485,12 @@
       <c r="P16" s="29">
         <v>-80.236925442144098</v>
       </c>
+      <c r="Q16" t="s">
+        <v>55</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0.1</v>
+      </c>
       <c r="X16"/>
       <c r="Y16"/>
     </row>
@@ -19523,6 +19541,12 @@
       </c>
       <c r="P17" s="32">
         <v>-82.7220401338042</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>56</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0.2</v>
       </c>
       <c r="X17"/>
       <c r="Y17"/>
@@ -19532,22 +19556,22 @@
     </row>
     <row r="19" spans="2:25">
       <c r="S19" s="1"/>
-      <c r="T19" s="61" t="s">
+      <c r="T19" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="U19" s="61"/>
-      <c r="V19" s="61"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
       <c r="W19" s="1"/>
     </row>
     <row r="20" spans="2:25">
-      <c r="K20" s="59" t="s">
+      <c r="K20" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
       <c r="Q20" s="10" t="s">
         <v>2</v>
       </c>
@@ -19666,7 +19690,7 @@
       <c r="Q23" s="18">
         <v>0.16553407200072537</v>
       </c>
-      <c r="R23" s="10" t="s">
+      <c r="R23" s="60" t="s">
         <v>28</v>
       </c>
       <c r="S23" s="19">
@@ -19845,33 +19869,33 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B1:AD36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <dimension ref="B1:AC36"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="1.125" customWidth="1"/>
-    <col min="2" max="2" width="8.375" customWidth="1"/>
-    <col min="3" max="10" width="4.375" customWidth="1"/>
-    <col min="11" max="15" width="7.625" customWidth="1"/>
+    <col min="1" max="1" width="1.08203125" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="3" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="15" width="7.58203125" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.625" customWidth="1"/>
-    <col min="19" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="9.875" customWidth="1"/>
-    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.58203125" customWidth="1"/>
+    <col min="19" max="22" width="8.83203125" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" customWidth="1"/>
+    <col min="24" max="25" width="6.08203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.58203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.125" customWidth="1"/>
+    <col min="28" max="28" width="5.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30">
+    <row r="1" spans="2:29">
       <c r="B1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AB1" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="61"/>
+      <c r="AC1" s="63"/>
     </row>
-    <row r="2" spans="2:30">
+    <row r="2" spans="2:29">
       <c r="B2" t="s">
         <v>31</v>
       </c>
@@ -19879,19 +19903,16 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="AA2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AB2" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="AC2" s="64">
+      <c r="AC2" s="59">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AD2">
-        <v>0.14000000000000001</v>
-      </c>
     </row>
-    <row r="3" spans="2:30">
+    <row r="3" spans="2:29">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -19899,19 +19920,16 @@
         <v>0.02</v>
       </c>
       <c r="AA3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AB3" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AC3" s="64">
+      <c r="AC3" s="59">
         <v>0.02</v>
       </c>
-      <c r="AD3">
-        <v>0.02</v>
-      </c>
     </row>
-    <row r="4" spans="2:30">
+    <row r="4" spans="2:29">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -19923,38 +19941,38 @@
         <v>25</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62" t="s">
+      <c r="J4" s="64"/>
+      <c r="K4" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62" t="s">
+      <c r="L4" s="64"/>
+      <c r="M4" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="62"/>
-      <c r="O4" s="60" t="s">
+      <c r="N4" s="64"/>
+      <c r="O4" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60" t="s">
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60" t="s">
+      <c r="R4" s="62"/>
+      <c r="S4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60" t="s">
+      <c r="T4" s="62"/>
+      <c r="U4" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="60"/>
+      <c r="V4" s="62"/>
       <c r="W4" s="3"/>
       <c r="X4" s="2" t="s">
         <v>27</v>
@@ -19962,7 +19980,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:30">
+    <row r="5" spans="2:29">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -20042,7 +20060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:30">
+    <row r="6" spans="2:29">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -20131,7 +20149,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="2:30">
+    <row r="7" spans="2:29">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -20220,7 +20238,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="2:30">
+    <row r="8" spans="2:29">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -20309,7 +20327,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:30">
+    <row r="9" spans="2:29">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -20398,7 +20416,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="2:30">
+    <row r="10" spans="2:29">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -20487,7 +20505,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="2:30">
+    <row r="11" spans="2:29">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -20576,7 +20594,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="2:30">
+    <row r="12" spans="2:29">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -20659,7 +20677,7 @@
         <v>-1.3391316716759885</v>
       </c>
     </row>
-    <row r="13" spans="2:30">
+    <row r="13" spans="2:29">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -20742,7 +20760,7 @@
         <v>-2.5273619887352097</v>
       </c>
     </row>
-    <row r="14" spans="2:30">
+    <row r="14" spans="2:29">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -20825,7 +20843,7 @@
         <v>-1.8483288249870145</v>
       </c>
     </row>
-    <row r="15" spans="2:30">
+    <row r="15" spans="2:29">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -20908,7 +20926,7 @@
         <v>-5.5079185398582702</v>
       </c>
     </row>
-    <row r="16" spans="2:30">
+    <row r="16" spans="2:29">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -21078,32 +21096,29 @@
       <c r="W18" s="1"/>
     </row>
     <row r="19" spans="2:26">
-      <c r="U19" s="63" t="s">
+      <c r="U19" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="V19" s="63"/>
+      <c r="V19" s="65"/>
       <c r="W19" s="1"/>
     </row>
     <row r="20" spans="2:26">
       <c r="C20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="59" t="s">
+      <c r="K20" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
       <c r="Q20" s="10" t="s">
         <v>2</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>1</v>
-      </c>
-      <c r="V20" t="s">
-        <v>53</v>
       </c>
       <c r="W20" s="1"/>
     </row>
@@ -21139,7 +21154,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="18">
-        <v>0.11292431200074263</v>
+        <v>0.11292431200074265</v>
       </c>
       <c r="S21" s="19">
         <f t="array" ref="S21:S32">MMULT(K21:P32,Q21:Q26)</f>
@@ -21150,11 +21165,9 @@
       </c>
       <c r="U21" s="2">
         <f>-Q22*L28</f>
-        <v>0.33338870753021377</v>
-      </c>
-      <c r="V21" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.33338870753021366</v>
+      </c>
+      <c r="V21" s="8"/>
       <c r="W21" s="8"/>
     </row>
     <row r="22" spans="2:26">
@@ -21185,21 +21198,19 @@
         <v>0</v>
       </c>
       <c r="Q22" s="18">
-        <v>0.21208618204515853</v>
+        <v>0.21208618204515844</v>
       </c>
       <c r="S22" s="19">
-        <v>0.20000000000000007</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="T22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="U22" s="1">
         <f>-K22*Q21</f>
-        <v>0.27326331255219577</v>
-      </c>
-      <c r="V22" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.27326331255219583</v>
+      </c>
+      <c r="V22" s="8"/>
       <c r="W22" s="9"/>
     </row>
     <row r="23" spans="2:26">
@@ -21231,24 +21242,22 @@
         <v>4.5787414372637594</v>
       </c>
       <c r="Q23" s="18">
-        <v>0.16553407200072537</v>
+        <v>0.16553407200072545</v>
       </c>
       <c r="R23" s="10" t="s">
         <v>28</v>
       </c>
       <c r="S23" s="19">
-        <v>0.28386968674528629</v>
+        <v>0.28386968674528656</v>
       </c>
       <c r="T23" s="6" t="s">
         <v>52</v>
       </c>
       <c r="U23" s="1">
         <f>Q24*O16</f>
-        <v>0.48487038977007496</v>
-      </c>
-      <c r="V23" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.48487038977007502</v>
+      </c>
+      <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
     <row r="24" spans="2:26">
@@ -21279,21 +21288,19 @@
         <v>0</v>
       </c>
       <c r="Q24" s="18">
-        <v>0.18386553924632076</v>
+        <v>0.18386553924632079</v>
       </c>
       <c r="S24" s="19">
-        <v>0.20000000000000007</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="T24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="U24" s="1">
         <f>-M24*Q23</f>
-        <v>0.42908147743086456</v>
-      </c>
-      <c r="V24" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.42908147743086478</v>
+      </c>
+      <c r="V24" s="8"/>
       <c r="W24" s="9"/>
     </row>
     <row r="25" spans="2:26">
@@ -21328,21 +21335,19 @@
         <v>-3.9783289202967236</v>
       </c>
       <c r="Q25" s="18">
-        <v>0.16101158429892443</v>
+        <v>0.16101158429892423</v>
       </c>
       <c r="S25" s="19">
-        <v>0.64751185464639349</v>
+        <v>0.6475118546463926</v>
       </c>
       <c r="T25" s="6" t="s">
         <v>51</v>
       </c>
       <c r="U25" s="1">
         <f>-P32*Q26</f>
-        <v>0.32151038697485096</v>
-      </c>
-      <c r="V25" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.32151038697485107</v>
+      </c>
+      <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
     <row r="26" spans="2:26">
@@ -21373,21 +21378,19 @@
         <v>0</v>
       </c>
       <c r="Q26" s="18">
-        <v>0.15399490886064554</v>
+        <v>0.1539949088606456</v>
       </c>
       <c r="S26" s="19">
-        <v>0.2</v>
+        <v>0.20000000000000062</v>
       </c>
       <c r="T26" s="6" t="s">
         <v>50</v>
       </c>
       <c r="U26" s="4">
         <f>-O26*Q25</f>
-        <v>0.26753186866431033</v>
-      </c>
-      <c r="V26" s="8">
-        <v>0.5</v>
-      </c>
+        <v>0.26753186866431</v>
+      </c>
+      <c r="V26" s="8"/>
     </row>
     <row r="27" spans="2:26">
       <c r="C27" t="s">
@@ -21421,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="19">
-        <v>0.70004040540572343</v>
+        <v>0.7000404054057221</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -21452,7 +21455,13 @@
         <v>0</v>
       </c>
       <c r="S28" s="19">
-        <v>0.19999999999999996</v>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="T28" t="s">
+        <v>54</v>
+      </c>
+      <c r="U28">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -21484,7 +21493,13 @@
         <v>4.005616072115366</v>
       </c>
       <c r="S29" s="19">
-        <v>0.1999999999999999</v>
+        <v>0.20000000000000012</v>
+      </c>
+      <c r="T29" t="s">
+        <v>55</v>
+      </c>
+      <c r="U29">
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -21517,6 +21532,12 @@
       <c r="S30" s="19">
         <v>0.35595039650151911</v>
       </c>
+      <c r="T30" t="s">
+        <v>56</v>
+      </c>
+      <c r="U30">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="31" spans="2:26">
       <c r="C31" t="s">
@@ -21550,7 +21571,7 @@
         <v>1.8483288249870145</v>
       </c>
       <c r="S31" s="19">
-        <v>0.97063504577823023</v>
+        <v>0.97063504577823134</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -21581,7 +21602,7 @@
         <v>-2.0877988068150684</v>
       </c>
       <c r="S32" s="19">
-        <v>0.20000000000000012</v>
+        <v>0.19999999999999979</v>
       </c>
     </row>
     <row r="35" spans="18:23">

--- a/DOCP_optimization_3bus_example.xlsx
+++ b/DOCP_optimization_3bus_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\GitHub\Optimal_DOCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F7E2EF-78E9-455A-8CF4-9C57A4110E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C52C60-46A6-45F5-8C18-915A954B3B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
   </bookViews>
   <sheets>
     <sheet name="Three_bus_without_transients" sheetId="4" r:id="rId1"/>
@@ -855,8 +855,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8743043" y="575128"/>
-          <a:ext cx="4697659" cy="1924134"/>
+          <a:off x="8797018" y="581478"/>
+          <a:ext cx="4723059" cy="1955884"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -9851,8 +9851,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7469565" y="7052279"/>
-          <a:ext cx="4700986" cy="1913551"/>
+          <a:off x="7522482" y="7144884"/>
+          <a:ext cx="4722152" cy="1940009"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -18687,13 +18687,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>148166</xdr:colOff>
+      <xdr:colOff>124353</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>179916</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>243414</xdr:colOff>
+      <xdr:colOff>219601</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>151983</xdr:rowOff>
     </xdr:to>
@@ -18718,8 +18718,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1195916" y="6614583"/>
-          <a:ext cx="5990165" cy="4194817"/>
+          <a:off x="1180041" y="6529916"/>
+          <a:ext cx="6008685" cy="4139255"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18732,7 +18732,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -19032,20 +19032,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:Y37"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="1.08203125" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
-    <col min="3" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="15" width="7.58203125" customWidth="1"/>
+    <col min="1" max="1" width="1.125" customWidth="1"/>
+    <col min="2" max="2" width="8.375" customWidth="1"/>
+    <col min="3" max="10" width="4.375" customWidth="1"/>
+    <col min="11" max="15" width="7.625" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.58203125" customWidth="1"/>
-    <col min="19" max="22" width="8.83203125" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" customWidth="1"/>
-    <col min="24" max="25" width="6.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.625" customWidth="1"/>
+    <col min="19" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="9.875" customWidth="1"/>
+    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.08203125" customWidth="1"/>
+    <col min="28" max="28" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
@@ -19870,20 +19870,20 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B1:AC36"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="1.08203125" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
-    <col min="3" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="15" width="7.58203125" customWidth="1"/>
+    <col min="1" max="1" width="1.125" customWidth="1"/>
+    <col min="2" max="2" width="8.375" customWidth="1"/>
+    <col min="3" max="10" width="4.375" customWidth="1"/>
+    <col min="11" max="15" width="7.625" customWidth="1"/>
     <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="18" width="7.58203125" customWidth="1"/>
-    <col min="19" max="22" width="8.83203125" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" customWidth="1"/>
-    <col min="24" max="25" width="6.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.625" customWidth="1"/>
+    <col min="19" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="9.875" customWidth="1"/>
+    <col min="24" max="25" width="6.125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="2.5" customWidth="1"/>
-    <col min="28" max="28" width="5.08203125" customWidth="1"/>
+    <col min="28" max="28" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:29">
@@ -21133,8 +21133,8 @@
         <v>1</v>
       </c>
       <c r="K21" s="11">
-        <f>W9</f>
-        <v>-2.7691675289173658</v>
+        <f>Z9</f>
+        <v>-2.2105209071486667</v>
       </c>
       <c r="L21" s="12">
         <f>-Q9</f>
@@ -21154,18 +21154,18 @@
         <v>0</v>
       </c>
       <c r="Q21" s="18">
-        <v>0.11292431200074265</v>
+        <v>0.11292431200074263</v>
       </c>
       <c r="S21" s="19">
         <f t="array" ref="S21:S32">MMULT(K21:P32,Q21:Q26)</f>
-        <v>0.32163183147068763</v>
+        <v>0.384716616885457</v>
       </c>
       <c r="T21" s="57" t="s">
         <v>47</v>
       </c>
       <c r="U21" s="2">
         <f>-Q22*L28</f>
-        <v>0.33338870753021366</v>
+        <v>0.33338870753021377</v>
       </c>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
@@ -21198,17 +21198,17 @@
         <v>0</v>
       </c>
       <c r="Q22" s="18">
-        <v>0.21208618204515844</v>
+        <v>0.21208618204515853</v>
       </c>
       <c r="S22" s="19">
-        <v>0.1999999999999994</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="T22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="U22" s="1">
         <f>-K22*Q21</f>
-        <v>0.27326331255219583</v>
+        <v>0.27326331255219577</v>
       </c>
       <c r="V22" s="8"/>
       <c r="W22" s="9"/>
@@ -21242,20 +21242,20 @@
         <v>4.5787414372637594</v>
       </c>
       <c r="Q23" s="18">
-        <v>0.16553407200072545</v>
+        <v>0.16553407200072537</v>
       </c>
       <c r="R23" s="10" t="s">
         <v>28</v>
       </c>
       <c r="S23" s="19">
-        <v>0.28386968674528656</v>
+        <v>0.28386968674528629</v>
       </c>
       <c r="T23" s="6" t="s">
         <v>52</v>
       </c>
       <c r="U23" s="1">
         <f>Q24*O16</f>
-        <v>0.48487038977007502</v>
+        <v>0.48487038977007496</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
@@ -21288,17 +21288,17 @@
         <v>0</v>
       </c>
       <c r="Q24" s="18">
-        <v>0.18386553924632079</v>
+        <v>0.18386553924632076</v>
       </c>
       <c r="S24" s="19">
-        <v>0.19999999999999996</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="T24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="U24" s="1">
         <f>-M24*Q23</f>
-        <v>0.42908147743086478</v>
+        <v>0.42908147743086456</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="9"/>
@@ -21335,17 +21335,17 @@
         <v>-3.9783289202967236</v>
       </c>
       <c r="Q25" s="18">
-        <v>0.16101158429892423</v>
+        <v>0.16101158429892443</v>
       </c>
       <c r="S25" s="19">
-        <v>0.6475118546463926</v>
+        <v>0.64751185464639349</v>
       </c>
       <c r="T25" s="6" t="s">
         <v>51</v>
       </c>
       <c r="U25" s="1">
         <f>-P32*Q26</f>
-        <v>0.32151038697485107</v>
+        <v>0.32151038697485096</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
@@ -21378,17 +21378,17 @@
         <v>0</v>
       </c>
       <c r="Q26" s="18">
-        <v>0.1539949088606456</v>
+        <v>0.15399490886064554</v>
       </c>
       <c r="S26" s="19">
-        <v>0.20000000000000062</v>
+        <v>0.2</v>
       </c>
       <c r="T26" s="6" t="s">
         <v>50</v>
       </c>
       <c r="U26" s="4">
         <f>-O26*Q25</f>
-        <v>0.26753186866431</v>
+        <v>0.26753186866431033</v>
       </c>
       <c r="V26" s="8"/>
     </row>
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="19">
-        <v>0.7000404054057221</v>
+        <v>0.70004040540572343</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -21455,7 +21455,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="19">
-        <v>0.20000000000000007</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="T28" t="s">
         <v>54</v>
@@ -21493,7 +21493,7 @@
         <v>4.005616072115366</v>
       </c>
       <c r="S29" s="19">
-        <v>0.20000000000000012</v>
+        <v>0.1999999999999999</v>
       </c>
       <c r="T29" t="s">
         <v>55</v>
@@ -21571,7 +21571,7 @@
         <v>1.8483288249870145</v>
       </c>
       <c r="S31" s="19">
-        <v>0.97063504577823134</v>
+        <v>0.97063504577823023</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -21602,7 +21602,7 @@
         <v>-2.0877988068150684</v>
       </c>
       <c r="S32" s="19">
-        <v>0.19999999999999979</v>
+        <v>0.20000000000000012</v>
       </c>
     </row>
     <row r="35" spans="18:23">
@@ -21624,17 +21624,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="K20:P20"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
